--- a/tools/config/drop_table.xlsx
+++ b/tools/config/drop_table.xlsx
@@ -102,7 +102,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -125,13 +125,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
@@ -276,7 +269,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="40">
+  <fills count="39">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -334,12 +327,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -636,67 +623,70 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="11" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="11" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="12" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="11" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -711,73 +701,70 @@
     <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1293,7 +1280,7 @@
         <v>0.3</v>
       </c>
       <c r="F6" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G6" s="6">
         <v>1</v>
